--- a/output/pdf_financials_xlsx/ASCU.xlsx
+++ b/output/pdf_financials_xlsx/ASCU.xlsx
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>13.059</v>
+        <v>-13.059</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7.121</v>
+        <v>-7.121</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>6.989</v>
+        <v>-6.989</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>7.44</v>
+        <v>-7.44</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4.965</v>
+        <v>-4.965</v>
       </c>
     </row>
     <row r="17">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>13.059</v>
+        <v>-13.059</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>7.121</v>
+        <v>-7.121</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>6.989</v>
+        <v>-6.989</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>7.44</v>
+        <v>-7.44</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>4.965</v>
+        <v>-4.965</v>
       </c>
     </row>
     <row r="21">
@@ -1035,19 +1035,19 @@
         <v>-5.104</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>13.059</v>
+        <v>-13.059</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>7.121</v>
+        <v>-7.121</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6.989</v>
+        <v>-6.989</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>7.44</v>
+        <v>-7.44</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4.965</v>
+        <v>-4.965</v>
       </c>
     </row>
     <row r="24">
@@ -1116,19 +1116,19 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>45.031034</v>
+        <v>-45.031034</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>79.12222199999999</v>
+        <v>-79.12222199999999</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>99.842857</v>
+        <v>-99.842857</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>124</v>
+        <v>-124</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>165.5</v>
+        <v>-165.5</v>
       </c>
     </row>
     <row r="27">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>13.059</v>
+        <v>-13.059</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7.121</v>
+        <v>-7.121</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6.989</v>
+        <v>-6.989</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7.44</v>
+        <v>-7.44</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.965</v>
+        <v>-4.965</v>
       </c>
     </row>
     <row r="28">
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>13.134</v>
+        <v>-12.984</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>7.205</v>
+        <v>-7.037</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>7.052</v>
+        <v>-6.926</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.506</v>
+        <v>-7.374</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>4.996</v>
+        <v>-4.934</v>
       </c>
     </row>
     <row r="30">
@@ -1261,19 +1261,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.277</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>5.369</v>
@@ -6784,7 +6784,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>2.277</v>
       </c>
@@ -11375,13 +11379,13 @@
         </is>
       </c>
       <c r="H166" s="5" t="n">
-        <v>6.989</v>
+        <v>-6.989</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>7.44</v>
+        <v>-7.44</v>
       </c>
       <c r="J166" s="5" t="n">
-        <v>4.965</v>
+        <v>-4.965</v>
       </c>
     </row>
     <row r="167">
@@ -12591,10 +12595,10 @@
         </is>
       </c>
       <c r="F194" s="5" t="n">
-        <v>13.059</v>
+        <v>-13.059</v>
       </c>
       <c r="G194" s="5" t="n">
-        <v>7.121</v>
+        <v>-7.121</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ASCU.xlsx
+++ b/output/pdf_financials_xlsx/ASCU.xlsx
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.316</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.859</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-1.065</v>
       </c>
     </row>
     <row r="13">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-13.059</v>
+        <v>-13.048</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.121</v>
+        <v>-6.805</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.989</v>
+        <v>-6.13</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-7.44</v>
+        <v>-6.84</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.965</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="28">
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-12.984</v>
+        <v>-12.973</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.037</v>
+        <v>-6.721</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.926</v>
+        <v>-6.067</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.374</v>
+        <v>-6.774</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.934</v>
+        <v>-3.869</v>
       </c>
     </row>
     <row r="30">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>7.248</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>27.307</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>19.862</v>
@@ -1339,10 +1339,10 @@
         <v>10.494</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>31.741</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>104.754</v>
       </c>
     </row>
     <row r="35">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>7.248</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>27.307</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>20.026</v>
@@ -1389,10 +1389,10 @@
         <v>10.494</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>31.741</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>104.754</v>
       </c>
     </row>
     <row r="37">
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>2.052</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>27.425</v>
+        <v>0.118</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -1689,10 +1689,10 @@
         <v>0.157</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>31.911</v>
+        <v>0.17</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>105.334</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="49">
@@ -3586,19 +3586,19 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.048</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.064</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.064</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.059</v>
       </c>
     </row>
     <row r="125">
@@ -3611,19 +3611,19 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.048</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.064</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.064</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.059</v>
       </c>
     </row>
     <row r="126">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
@@ -7776,7 +7776,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -11136,7 +11140,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -12182,7 +12186,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">

--- a/output/pdf_financials_xlsx/ASCU.xlsx
+++ b/output/pdf_financials_xlsx/ASCU.xlsx
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.466</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>0.596</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="8">
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.466</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.596</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="11">
@@ -2167,19 +2167,19 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.613</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>2.474</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>7.012</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>2.018</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="68">
@@ -3070,10 +3070,10 @@
         <v>0</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="104">
@@ -3145,10 +3145,10 @@
         <v>-5.633</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-5.835</v>
+        <v>-5.848</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.649</v>
+        <v>-1.059</v>
       </c>
     </row>
     <row r="107">
@@ -3233,22 +3233,22 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>1.226</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>2.771</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.233</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>-0.462</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.644</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="111">
@@ -3751,16 +3751,16 @@
         <v>7.248</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>27.127</v>
+        <v>27.307</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>19.78</v>
+        <v>19.862</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>9.31</v>
+        <v>10.494</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>32.414</v>
+        <v>31.741</v>
       </c>
     </row>
     <row r="131">
@@ -7012,7 +7012,11 @@
           <t>Accretion 6</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -7236,7 +7240,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -7952,7 +7960,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -8080,7 +8092,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -8842,7 +8858,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -9960,7 +9980,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E135" s="5" t="n">
         <v>1.226</v>
       </c>
@@ -10872,7 +10896,11 @@
           <t>Directors' fees 11</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -11836,7 +11864,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
